--- a/artfynd/A 814-2022 artfynd.xlsx
+++ b/artfynd/A 814-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 814-2022 artfynd.xlsx
+++ b/artfynd/A 814-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1036,7 +1036,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>108284656</v>
+        <v>108284652</v>
       </c>
       <c r="B5" t="n">
         <v>56395</v>
@@ -1078,10 +1078,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>445042.7275985021</v>
+        <v>445035.2138796767</v>
       </c>
       <c r="R5" t="n">
-        <v>7065827.508636134</v>
+        <v>7065880.396477842</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1152,125 +1152,6 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>108284652</v>
-      </c>
-      <c r="B6" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Finnsäter N, Jmt</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>445035.2138796767</v>
-      </c>
-      <c r="R6" t="n">
-        <v>7065880.396477842</v>
-      </c>
-      <c r="S6" t="n">
-        <v>10</v>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2023-04-19</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2023-04-19</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>ringhack</t>
-        </is>
-      </c>
-      <c r="AD6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 814-2022 artfynd.xlsx
+++ b/artfynd/A 814-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>108284655</v>
+        <v>108284657</v>
       </c>
       <c r="B2" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -711,16 +706,18 @@
       <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Finnsäter N, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>445045.8341384493</v>
+        <v>444984</v>
       </c>
       <c r="R2" t="n">
-        <v>7065827.454555529</v>
+        <v>7065753</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,24 +747,14 @@
           <t>2023-04-19</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-04-19</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,15 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>108284654</v>
+        <v>108284670</v>
       </c>
       <c r="B3" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -810,38 +792,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Finnsäter N, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>445043.6306127341</v>
+        <v>445106</v>
       </c>
       <c r="R3" t="n">
-        <v>7065828.379595485</v>
+        <v>7065924</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,24 +849,9 @@
           <t>2023-04-19</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-04-19</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,15 +878,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>108284657</v>
+        <v>108284672</v>
       </c>
       <c r="B4" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -931,38 +889,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Finnsäter N, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>444984.6015222357</v>
+        <v>445107</v>
       </c>
       <c r="R4" t="n">
-        <v>7065752.709014866</v>
+        <v>7065924</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -992,24 +946,9 @@
           <t>2023-04-19</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-04-19</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1039,12 +978,7 @@
         <v>108284652</v>
       </c>
       <c r="B5" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1078,10 +1012,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>445035.2138796767</v>
+        <v>445035</v>
       </c>
       <c r="R5" t="n">
-        <v>7065880.396477842</v>
+        <v>7065880</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1111,19 +1045,9 @@
           <t>2023-04-19</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-04-19</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1152,6 +1076,425 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>108284654</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Finnsäter N, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>445043</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7065829</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-04-19</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-04-19</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>108284655</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Finnsäter N, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>445046</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7065827</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-04-19</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-04-19</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>ringhack</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>108284656</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Finnsäter N, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>445043</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7065827</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-04-19</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-04-19</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>ringhack</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>108284668</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Finnsäter N, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>445071</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7065873</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2023-04-19</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2023-04-19</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 814-2022 artfynd.xlsx
+++ b/artfynd/A 814-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108284670</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108284672</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -970,6 +985,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108284652</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108284654</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1180,6 +1205,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108284655</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1284,6 +1314,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108284656</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1390,6 +1425,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108284657</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1495,8 +1535,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108284668</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>